--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127245446</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127249686</v>
+        <v>127249538</v>
       </c>
       <c r="B2" t="n">
-        <v>96039</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -752,6 +760,11 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,52 +783,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127249538</v>
+        <v>127249686</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>96045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -862,11 +867,6 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -895,7 +895,7 @@
         <v>127245446</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1109,6 +1109,115 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127315058</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90760</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 34642, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>580524</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6385195</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -675,45 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127249538</v>
+        <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>96045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -758,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,37 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127249686</v>
+        <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>96045</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -865,6 +860,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127245446</v>
+        <v>127246074</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,13 +925,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>6385178</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127246074</v>
+        <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1035,13 +1034,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,7 +1054,7 @@
         <v>6385178</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,6 +1092,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
         <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>127315058</v>
       </c>
       <c r="B6" t="n">
-        <v>90760</v>
+        <v>90761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -675,37 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127249686</v>
+        <v>127249538</v>
       </c>
       <c r="B2" t="n">
-        <v>96046</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -750,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,45 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127249538</v>
+        <v>127249686</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>96046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -860,11 +865,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -675,45 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127249538</v>
+        <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>96050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -760,11 +752,6 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -783,44 +770,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127249686</v>
+        <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>96046</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -865,6 +860,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +895,7 @@
         <v>127246074</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>127315058</v>
       </c>
       <c r="B6" t="n">
-        <v>90761</v>
+        <v>90765</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
         <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127246074</v>
+        <v>127245446</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,13 +925,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>6385178</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,32 +1002,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127245446</v>
+        <v>127246074</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1034,13 +1035,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,7 +1055,7 @@
         <v>6385178</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1093,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -675,37 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127249686</v>
+        <v>127249538</v>
       </c>
       <c r="B2" t="n">
-        <v>96050</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -750,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,45 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127249538</v>
+        <v>127249686</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>96052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -862,11 +867,6 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -885,39 +885,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127245446</v>
+        <v>127246074</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,13 +925,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>6385178</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,39 +994,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127246074</v>
+        <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1035,13 +1034,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,7 +1054,7 @@
         <v>6385178</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,6 +1092,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
         <v>127315058</v>
       </c>
       <c r="B6" t="n">
-        <v>90765</v>
+        <v>90767</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -675,45 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127249538</v>
+        <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>96052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -758,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,37 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127249686</v>
+        <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>96052</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -867,6 +862,11 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>127315058</v>
       </c>
       <c r="B6" t="n">
-        <v>90767</v>
+        <v>90773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127246074</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
         <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
         <v>127315058</v>
       </c>
       <c r="B6" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127246074</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
         <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
         <v>127315058</v>
       </c>
       <c r="B6" t="n">
-        <v>90776</v>
+        <v>90784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
         <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>127315058</v>
       </c>
       <c r="B6" t="n">
-        <v>90784</v>
+        <v>90785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>96070</v>
+        <v>96039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127246074</v>
+        <v>127245446</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,13 +925,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>6385178</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,32 +1002,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127245446</v>
+        <v>127246074</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1034,13 +1035,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,7 +1055,7 @@
         <v>6385178</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1093,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,119 +1104,10 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>127315058</v>
-      </c>
-      <c r="B6" t="n">
-        <v>90786</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Fyrflikig jordstjärna</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Geastrum quadrifidum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>A 34642, Gölpefall, Sm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>580524</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6385195</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Hjorted</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127249686</v>
       </c>
       <c r="B2" t="n">
-        <v>96039</v>
+        <v>96070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127249538</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127245446</v>
+        <v>127246074</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,13 +925,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>6385178</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127246074</v>
+        <v>127245446</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1035,13 +1034,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,7 +1054,7 @@
         <v>6385178</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,6 +1092,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,10 +1104,119 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127315058</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90786</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 34642, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>580524</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6385195</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34644-2025 artfynd.xlsx
+++ b/artfynd/A 34644-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127249686</v>
+        <v>127250260</v>
       </c>
       <c r="B2" t="n">
-        <v>96070</v>
+        <v>91333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580516</v>
+        <v>580555</v>
       </c>
       <c r="R2" t="n">
-        <v>6385180</v>
+        <v>6385134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,60 +784,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127249538</v>
+        <v>127315058</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>91333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 34644, Gölpefall, Sm</t>
+          <t>A 34642, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580516</v>
+        <v>580524</v>
       </c>
       <c r="R3" t="n">
-        <v>6385180</v>
+        <v>6385195</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,46 +893,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127246074</v>
+        <v>127249686</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580537</v>
+        <v>580516</v>
       </c>
       <c r="R4" t="n">
-        <v>6385178</v>
+        <v>6385180</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,6 +976,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127245446</v>
+        <v>127246074</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1034,13 +1028,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,7 +1048,7 @@
         <v>6385178</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1086,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,59 +1104,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127315058</v>
+        <v>127245446</v>
       </c>
       <c r="B6" t="n">
-        <v>90786</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 34642, Gölpefall, Sm</t>
+          <t>A 34644, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580524</v>
+        <v>580537</v>
       </c>
       <c r="R6" t="n">
-        <v>6385195</v>
+        <v>6385178</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,10 +1207,482 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127246563</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 34644, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>580535</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6385202</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4 blommor</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127247492</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 34644, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>580546</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6385206</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>10 blommor</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127248527</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 34644, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>580527</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6385223</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6 blommor</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127249538</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 34644, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>580516</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6385180</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
